--- a/Team-Data/2013-14/3-6-2013-14.xlsx
+++ b/Team-Data/2013-14/3-6-2013-14.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -751,13 +818,13 @@
         <v>18</v>
       </c>
       <c r="AH2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AI2" t="n">
         <v>18</v>
       </c>
       <c r="AJ2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK2" t="n">
         <v>9</v>
@@ -811,7 +878,7 @@
         <v>26</v>
       </c>
       <c r="BB2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BC2" t="n">
         <v>16</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>3-6-2013-14</t>
+          <t>2014-03-06</t>
         </is>
       </c>
     </row>
@@ -921,13 +988,13 @@
         <v>-3.9</v>
       </c>
       <c r="AD3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AE3" t="n">
         <v>27</v>
       </c>
       <c r="AF3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AG3" t="n">
         <v>27</v>
@@ -969,13 +1036,13 @@
         <v>21</v>
       </c>
       <c r="AT3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AU3" t="n">
         <v>26</v>
       </c>
       <c r="AV3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AW3" t="n">
         <v>22</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>3-6-2013-14</t>
+          <t>2014-03-06</t>
         </is>
       </c>
     </row>
@@ -1115,7 +1182,7 @@
         <v>15</v>
       </c>
       <c r="AH4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AI4" t="n">
         <v>29</v>
@@ -1127,7 +1194,7 @@
         <v>15</v>
       </c>
       <c r="AL4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AM4" t="n">
         <v>12</v>
@@ -1160,7 +1227,7 @@
         <v>11</v>
       </c>
       <c r="AW4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AX4" t="n">
         <v>26</v>
@@ -1169,7 +1236,7 @@
         <v>8</v>
       </c>
       <c r="AZ4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BA4" t="n">
         <v>11</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>3-6-2013-14</t>
+          <t>2014-03-06</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1352,7 @@
         <v>-1.8</v>
       </c>
       <c r="AD5" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AE5" t="n">
         <v>17</v>
@@ -1354,7 +1421,7 @@
         <v>2</v>
       </c>
       <c r="BA5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BB5" t="n">
         <v>26</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>3-6-2013-14</t>
+          <t>2014-03-06</t>
         </is>
       </c>
     </row>
@@ -1467,7 +1534,7 @@
         <v>1</v>
       </c>
       <c r="AD6" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AE6" t="n">
         <v>11</v>
@@ -1515,7 +1582,7 @@
         <v>7</v>
       </c>
       <c r="AT6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AU6" t="n">
         <v>11</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>3-6-2013-14</t>
+          <t>2014-03-06</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1716,7 @@
         <v>-4.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE7" t="n">
         <v>20</v>
@@ -1688,7 +1755,7 @@
         <v>17</v>
       </c>
       <c r="AQ7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AR7" t="n">
         <v>3</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>3-6-2013-14</t>
+          <t>2014-03-06</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1898,7 @@
         <v>2.1</v>
       </c>
       <c r="AD8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE8" t="n">
         <v>9</v>
@@ -1843,7 +1910,7 @@
         <v>10</v>
       </c>
       <c r="AH8" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AI8" t="n">
         <v>2</v>
@@ -1852,7 +1919,7 @@
         <v>12</v>
       </c>
       <c r="AK8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AL8" t="n">
         <v>8</v>
@@ -1897,13 +1964,13 @@
         <v>4</v>
       </c>
       <c r="AZ8" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA8" t="n">
         <v>25</v>
       </c>
       <c r="BB8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BC8" t="n">
         <v>12</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>3-6-2013-14</t>
+          <t>2014-03-06</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2080,7 @@
         <v>-2.4</v>
       </c>
       <c r="AD9" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AE9" t="n">
         <v>18</v>
@@ -2043,7 +2110,7 @@
         <v>9</v>
       </c>
       <c r="AN9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AO9" t="n">
         <v>8</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>3-6-2013-14</t>
+          <t>2014-03-06</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2262,7 @@
         <v>-2.7</v>
       </c>
       <c r="AD10" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AE10" t="n">
         <v>20</v>
@@ -2207,7 +2274,7 @@
         <v>20</v>
       </c>
       <c r="AH10" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AI10" t="n">
         <v>6</v>
@@ -2216,7 +2283,7 @@
         <v>4</v>
       </c>
       <c r="AK10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AL10" t="n">
         <v>29</v>
@@ -2249,7 +2316,7 @@
         <v>20</v>
       </c>
       <c r="AV10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AW10" t="n">
         <v>4</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>3-6-2013-14</t>
+          <t>2014-03-06</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2444,7 @@
         <v>4.7</v>
       </c>
       <c r="AD11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE11" t="n">
         <v>8</v>
@@ -2392,7 +2459,7 @@
         <v>18</v>
       </c>
       <c r="AI11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AJ11" t="n">
         <v>5</v>
@@ -2431,7 +2498,7 @@
         <v>10</v>
       </c>
       <c r="AV11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AW11" t="n">
         <v>13</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>3-6-2013-14</t>
+          <t>2014-03-06</t>
         </is>
       </c>
     </row>
@@ -2559,10 +2626,10 @@
         <v>4.7</v>
       </c>
       <c r="AD12" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AE12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AF12" t="n">
         <v>5</v>
@@ -2592,7 +2659,7 @@
         <v>21</v>
       </c>
       <c r="AO12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AP12" t="n">
         <v>1</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>3-6-2013-14</t>
+          <t>2014-03-06</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>7.2</v>
       </c>
       <c r="AD13" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AE13" t="n">
         <v>1</v>
@@ -2753,7 +2820,7 @@
         <v>1</v>
       </c>
       <c r="AH13" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AI13" t="n">
         <v>21</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>3-6-2013-14</t>
+          <t>2014-03-06</t>
         </is>
       </c>
     </row>
@@ -2845,67 +2912,67 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E14" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F14" t="n">
         <v>20</v>
       </c>
       <c r="G14" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.677</v>
       </c>
       <c r="H14" t="n">
         <v>48.2</v>
       </c>
       <c r="I14" t="n">
-        <v>38.9</v>
+        <v>38.6</v>
       </c>
       <c r="J14" t="n">
-        <v>82.09999999999999</v>
+        <v>81.8</v>
       </c>
       <c r="K14" t="n">
-        <v>0.474</v>
+        <v>0.473</v>
       </c>
       <c r="L14" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>23.7</v>
+        <v>23.6</v>
       </c>
       <c r="N14" t="n">
-        <v>0.352</v>
+        <v>0.35</v>
       </c>
       <c r="O14" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="P14" t="n">
-        <v>29.6</v>
+        <v>29.7</v>
       </c>
       <c r="Q14" t="n">
         <v>0.729</v>
       </c>
       <c r="R14" t="n">
-        <v>10.5</v>
+        <v>10.4</v>
       </c>
       <c r="S14" t="n">
-        <v>32.8</v>
+        <v>32.5</v>
       </c>
       <c r="T14" t="n">
-        <v>43.2</v>
+        <v>42.9</v>
       </c>
       <c r="U14" t="n">
-        <v>24.4</v>
+        <v>24.2</v>
       </c>
       <c r="V14" t="n">
         <v>13.9</v>
       </c>
       <c r="W14" t="n">
-        <v>8.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="X14" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="Y14" t="n">
         <v>3.4</v>
@@ -2914,19 +2981,19 @@
         <v>21.6</v>
       </c>
       <c r="AA14" t="n">
-        <v>24</v>
+        <v>24.1</v>
       </c>
       <c r="AB14" t="n">
-        <v>107.7</v>
+        <v>107.2</v>
       </c>
       <c r="AC14" t="n">
-        <v>7.2</v>
+        <v>6.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AF14" t="n">
         <v>7</v>
@@ -2938,13 +3005,13 @@
         <v>23</v>
       </c>
       <c r="AI14" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AJ14" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AK14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AL14" t="n">
         <v>11</v>
@@ -2956,7 +3023,7 @@
         <v>23</v>
       </c>
       <c r="AO14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AP14" t="n">
         <v>2</v>
@@ -2968,19 +3035,19 @@
         <v>21</v>
       </c>
       <c r="AS14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AT14" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AU14" t="n">
         <v>3</v>
       </c>
       <c r="AV14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW14" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AX14" t="n">
         <v>18</v>
@@ -2995,10 +3062,10 @@
         <v>2</v>
       </c>
       <c r="BB14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BC14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BD14" t="n">
         <v>10</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>3-6-2013-14</t>
+          <t>2014-03-06</t>
         </is>
       </c>
     </row>
@@ -3027,37 +3094,37 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E15" t="n">
         <v>21</v>
       </c>
       <c r="F15" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G15" t="n">
-        <v>0.339</v>
+        <v>0.344</v>
       </c>
       <c r="H15" t="n">
         <v>48.1</v>
       </c>
       <c r="I15" t="n">
-        <v>37.7</v>
+        <v>37.8</v>
       </c>
       <c r="J15" t="n">
         <v>84</v>
       </c>
       <c r="K15" t="n">
-        <v>0.449</v>
+        <v>0.45</v>
       </c>
       <c r="L15" t="n">
         <v>9.4</v>
       </c>
       <c r="M15" t="n">
-        <v>24.6</v>
+        <v>24.5</v>
       </c>
       <c r="N15" t="n">
-        <v>0.381</v>
+        <v>0.384</v>
       </c>
       <c r="O15" t="n">
         <v>16.6</v>
@@ -3066,7 +3133,7 @@
         <v>22.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.749</v>
+        <v>0.75</v>
       </c>
       <c r="R15" t="n">
         <v>9.199999999999999</v>
@@ -3075,19 +3142,19 @@
         <v>32.4</v>
       </c>
       <c r="T15" t="n">
-        <v>41.5</v>
+        <v>41.7</v>
       </c>
       <c r="U15" t="n">
         <v>23.6</v>
       </c>
       <c r="V15" t="n">
-        <v>15.5</v>
+        <v>15.4</v>
       </c>
       <c r="W15" t="n">
         <v>6.9</v>
       </c>
       <c r="X15" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="Y15" t="n">
         <v>4.5</v>
@@ -3099,25 +3166,25 @@
         <v>19.1</v>
       </c>
       <c r="AB15" t="n">
-        <v>101.4</v>
+        <v>101.6</v>
       </c>
       <c r="AC15" t="n">
-        <v>-6</v>
+        <v>-5.3</v>
       </c>
       <c r="AD15" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AE15" t="n">
         <v>25</v>
       </c>
       <c r="AF15" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AG15" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AH15" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AI15" t="n">
         <v>16</v>
@@ -3126,16 +3193,16 @@
         <v>10</v>
       </c>
       <c r="AK15" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AL15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AM15" t="n">
         <v>6</v>
       </c>
       <c r="AN15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO15" t="n">
         <v>21</v>
@@ -3144,7 +3211,7 @@
         <v>19</v>
       </c>
       <c r="AQ15" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AR15" t="n">
         <v>25</v>
@@ -3159,7 +3226,7 @@
         <v>5</v>
       </c>
       <c r="AV15" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AW15" t="n">
         <v>26</v>
@@ -3171,13 +3238,13 @@
         <v>12</v>
       </c>
       <c r="AZ15" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BA15" t="n">
         <v>28</v>
       </c>
       <c r="BB15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BC15" t="n">
         <v>27</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>3-6-2013-14</t>
+          <t>2014-03-06</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>0.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AE16" t="n">
         <v>11</v>
@@ -3305,10 +3372,10 @@
         <v>17</v>
       </c>
       <c r="AJ16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AK16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AL16" t="n">
         <v>30</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>3-6-2013-14</t>
+          <t>2014-03-06</t>
         </is>
       </c>
     </row>
@@ -3391,46 +3458,46 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E17" t="n">
         <v>43</v>
       </c>
       <c r="F17" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G17" t="n">
-        <v>0.729</v>
+        <v>0.741</v>
       </c>
       <c r="H17" t="n">
         <v>48.4</v>
       </c>
       <c r="I17" t="n">
-        <v>39.2</v>
+        <v>39.3</v>
       </c>
       <c r="J17" t="n">
         <v>77</v>
       </c>
       <c r="K17" t="n">
-        <v>0.509</v>
+        <v>0.511</v>
       </c>
       <c r="L17" t="n">
         <v>8.1</v>
       </c>
       <c r="M17" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="N17" t="n">
-        <v>0.37</v>
+        <v>0.371</v>
       </c>
       <c r="O17" t="n">
         <v>17.9</v>
       </c>
       <c r="P17" t="n">
-        <v>23.6</v>
+        <v>23.7</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.758</v>
+        <v>0.757</v>
       </c>
       <c r="R17" t="n">
         <v>7.5</v>
@@ -3445,7 +3512,7 @@
         <v>23.2</v>
       </c>
       <c r="V17" t="n">
-        <v>14.8</v>
+        <v>14.7</v>
       </c>
       <c r="W17" t="n">
         <v>9.199999999999999</v>
@@ -3460,25 +3527,25 @@
         <v>20.2</v>
       </c>
       <c r="AA17" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="AB17" t="n">
-        <v>104.4</v>
+        <v>104.7</v>
       </c>
       <c r="AC17" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="AD17" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AE17" t="n">
         <v>4</v>
       </c>
       <c r="AF17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AG17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH17" t="n">
         <v>9</v>
@@ -3493,7 +3560,7 @@
         <v>1</v>
       </c>
       <c r="AL17" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AM17" t="n">
         <v>15</v>
@@ -3505,7 +3572,7 @@
         <v>14</v>
       </c>
       <c r="AP17" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AQ17" t="n">
         <v>16</v>
@@ -3535,16 +3602,16 @@
         <v>1</v>
       </c>
       <c r="AZ17" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA17" t="n">
         <v>13</v>
       </c>
       <c r="BB17" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BC17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BD17" t="n">
         <v>10</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>3-6-2013-14</t>
+          <t>2014-03-06</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>-8.199999999999999</v>
       </c>
       <c r="AD18" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AE18" t="n">
         <v>30</v>
@@ -3720,7 +3787,7 @@
         <v>18</v>
       </c>
       <c r="BA18" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BB18" t="n">
         <v>29</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>3-6-2013-14</t>
+          <t>2014-03-06</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3900,7 @@
         <v>3.8</v>
       </c>
       <c r="AD19" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AE19" t="n">
         <v>15</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>3-6-2013-14</t>
+          <t>2014-03-06</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4082,7 @@
         <v>-2.8</v>
       </c>
       <c r="AD20" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AE20" t="n">
         <v>20</v>
@@ -4069,7 +4136,7 @@
         <v>18</v>
       </c>
       <c r="AV20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AW20" t="n">
         <v>12</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>3-6-2013-14</t>
+          <t>2014-03-06</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4264,7 @@
         <v>-2.9</v>
       </c>
       <c r="AD21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE21" t="n">
         <v>23</v>
@@ -4239,7 +4306,7 @@
         <v>19</v>
       </c>
       <c r="AR21" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AS21" t="n">
         <v>27</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>3-6-2013-14</t>
+          <t>2014-03-06</t>
         </is>
       </c>
     </row>
@@ -4301,103 +4368,103 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E22" t="n">
         <v>46</v>
       </c>
       <c r="F22" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G22" t="n">
-        <v>0.742</v>
+        <v>0.754</v>
       </c>
       <c r="H22" t="n">
         <v>48.2</v>
       </c>
       <c r="I22" t="n">
-        <v>39.2</v>
+        <v>39.1</v>
       </c>
       <c r="J22" t="n">
-        <v>82.2</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="K22" t="n">
         <v>0.476</v>
       </c>
       <c r="L22" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="M22" t="n">
-        <v>21.1</v>
+        <v>20.9</v>
       </c>
       <c r="N22" t="n">
-        <v>0.359</v>
+        <v>0.358</v>
       </c>
       <c r="O22" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="P22" t="n">
-        <v>24.5</v>
+        <v>24.6</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.805</v>
+        <v>0.803</v>
       </c>
       <c r="R22" t="n">
         <v>11</v>
       </c>
       <c r="S22" t="n">
-        <v>34</v>
+        <v>34.1</v>
       </c>
       <c r="T22" t="n">
-        <v>45</v>
+        <v>45.1</v>
       </c>
       <c r="U22" t="n">
         <v>21.7</v>
       </c>
       <c r="V22" t="n">
-        <v>15.8</v>
+        <v>15.9</v>
       </c>
       <c r="W22" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="X22" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="Y22" t="n">
         <v>3.6</v>
       </c>
       <c r="Z22" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="AA22" t="n">
         <v>20.2</v>
       </c>
       <c r="AB22" t="n">
-        <v>105.7</v>
+        <v>105.4</v>
       </c>
       <c r="AC22" t="n">
-        <v>6.7</v>
+        <v>6.9</v>
       </c>
       <c r="AD22" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AE22" t="n">
         <v>1</v>
       </c>
       <c r="AF22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AG22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH22" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI22" t="n">
         <v>5</v>
       </c>
       <c r="AJ22" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AK22" t="n">
         <v>3</v>
@@ -4409,13 +4476,13 @@
         <v>16</v>
       </c>
       <c r="AN22" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AO22" t="n">
         <v>5</v>
       </c>
       <c r="AP22" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AQ22" t="n">
         <v>2</v>
@@ -4424,10 +4491,10 @@
         <v>17</v>
       </c>
       <c r="AS22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AT22" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AU22" t="n">
         <v>14</v>
@@ -4436,7 +4503,7 @@
         <v>28</v>
       </c>
       <c r="AW22" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AX22" t="n">
         <v>2</v>
@@ -4445,16 +4512,16 @@
         <v>3</v>
       </c>
       <c r="AZ22" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BA22" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BB22" t="n">
         <v>5</v>
       </c>
       <c r="BC22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BD22" t="n">
         <v>10</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>3-6-2013-14</t>
+          <t>2014-03-06</t>
         </is>
       </c>
     </row>
@@ -4606,7 +4673,7 @@
         <v>24</v>
       </c>
       <c r="AS23" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AT23" t="n">
         <v>19</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>3-6-2013-14</t>
+          <t>2014-03-06</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4810,7 @@
         <v>-11.2</v>
       </c>
       <c r="AD24" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AE24" t="n">
         <v>29</v>
@@ -4779,7 +4846,7 @@
         <v>18</v>
       </c>
       <c r="AP24" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ24" t="n">
         <v>28</v>
@@ -4809,7 +4876,7 @@
         <v>30</v>
       </c>
       <c r="AZ24" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BA24" t="n">
         <v>12</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>3-6-2013-14</t>
+          <t>2014-03-06</t>
         </is>
       </c>
     </row>
@@ -4847,46 +4914,46 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E25" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F25" t="n">
         <v>25</v>
       </c>
       <c r="G25" t="n">
-        <v>0.59</v>
+        <v>0.583</v>
       </c>
       <c r="H25" t="n">
-        <v>48.2</v>
+        <v>48.3</v>
       </c>
       <c r="I25" t="n">
         <v>38.7</v>
       </c>
       <c r="J25" t="n">
-        <v>84.09999999999999</v>
+        <v>84.2</v>
       </c>
       <c r="K25" t="n">
-        <v>0.46</v>
+        <v>0.459</v>
       </c>
       <c r="L25" t="n">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="M25" t="n">
-        <v>25.1</v>
+        <v>25</v>
       </c>
       <c r="N25" t="n">
-        <v>0.375</v>
+        <v>0.372</v>
       </c>
       <c r="O25" t="n">
-        <v>18.7</v>
+        <v>18.5</v>
       </c>
       <c r="P25" t="n">
-        <v>24.6</v>
+        <v>24.4</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.758</v>
+        <v>0.759</v>
       </c>
       <c r="R25" t="n">
         <v>11.6</v>
@@ -4901,34 +4968,34 @@
         <v>19.3</v>
       </c>
       <c r="V25" t="n">
-        <v>15.2</v>
+        <v>15.3</v>
       </c>
       <c r="W25" t="n">
         <v>8.4</v>
       </c>
       <c r="X25" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="Y25" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="Z25" t="n">
         <v>22</v>
       </c>
       <c r="AA25" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="AB25" t="n">
-        <v>105.5</v>
+        <v>105.2</v>
       </c>
       <c r="AC25" t="n">
         <v>2.8</v>
       </c>
       <c r="AD25" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="AE25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF25" t="n">
         <v>9</v>
@@ -4940,16 +5007,16 @@
         <v>19</v>
       </c>
       <c r="AI25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AJ25" t="n">
         <v>9</v>
       </c>
       <c r="AK25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AL25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AM25" t="n">
         <v>3</v>
@@ -4961,7 +5028,7 @@
         <v>10</v>
       </c>
       <c r="AP25" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AQ25" t="n">
         <v>15</v>
@@ -4982,7 +5049,7 @@
         <v>21</v>
       </c>
       <c r="AW25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AX25" t="n">
         <v>14</v>
@@ -4994,7 +5061,7 @@
         <v>25</v>
       </c>
       <c r="BA25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BB25" t="n">
         <v>6</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>3-6-2013-14</t>
+          <t>2014-03-06</t>
         </is>
       </c>
     </row>
@@ -5107,10 +5174,10 @@
         <v>5.2</v>
       </c>
       <c r="AD26" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AE26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AF26" t="n">
         <v>5</v>
@@ -5179,7 +5246,7 @@
         <v>14</v>
       </c>
       <c r="BB26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BC26" t="n">
         <v>6</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>3-6-2013-14</t>
+          <t>2014-03-06</t>
         </is>
       </c>
     </row>
@@ -5289,7 +5356,7 @@
         <v>-2.1</v>
       </c>
       <c r="AD27" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AE27" t="n">
         <v>23</v>
@@ -5310,7 +5377,7 @@
         <v>16</v>
       </c>
       <c r="AK27" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AL27" t="n">
         <v>24</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>3-6-2013-14</t>
+          <t>2014-03-06</t>
         </is>
       </c>
     </row>
@@ -5393,22 +5460,22 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E28" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F28" t="n">
         <v>16</v>
       </c>
       <c r="G28" t="n">
-        <v>0.738</v>
+        <v>0.733</v>
       </c>
       <c r="H28" t="n">
-        <v>48.2</v>
+        <v>48.3</v>
       </c>
       <c r="I28" t="n">
-        <v>40.1</v>
+        <v>40.2</v>
       </c>
       <c r="J28" t="n">
         <v>82.3</v>
@@ -5426,28 +5493,28 @@
         <v>0.391</v>
       </c>
       <c r="O28" t="n">
-        <v>16</v>
+        <v>15.9</v>
       </c>
       <c r="P28" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.79</v>
+        <v>0.789</v>
       </c>
       <c r="R28" t="n">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="S28" t="n">
         <v>33.5</v>
       </c>
       <c r="T28" t="n">
-        <v>42.5</v>
+        <v>42.4</v>
       </c>
       <c r="U28" t="n">
         <v>24.9</v>
       </c>
       <c r="V28" t="n">
-        <v>14.9</v>
+        <v>14.8</v>
       </c>
       <c r="W28" t="n">
         <v>7.4</v>
@@ -5465,22 +5532,22 @@
         <v>19.6</v>
       </c>
       <c r="AB28" t="n">
-        <v>104.4</v>
+        <v>104.3</v>
       </c>
       <c r="AC28" t="n">
-        <v>6.5</v>
+        <v>6.2</v>
       </c>
       <c r="AD28" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="AE28" t="n">
         <v>3</v>
       </c>
       <c r="AF28" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AG28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH28" t="n">
         <v>19</v>
@@ -5495,7 +5562,7 @@
         <v>2</v>
       </c>
       <c r="AL28" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AM28" t="n">
         <v>17</v>
@@ -5519,7 +5586,7 @@
         <v>6</v>
       </c>
       <c r="AT28" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AU28" t="n">
         <v>2</v>
@@ -5543,10 +5610,10 @@
         <v>23</v>
       </c>
       <c r="BB28" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BC28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BD28" t="n">
         <v>10</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>3-6-2013-14</t>
+          <t>2014-03-06</t>
         </is>
       </c>
     </row>
@@ -5701,7 +5768,7 @@
         <v>20</v>
       </c>
       <c r="AT29" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AU29" t="n">
         <v>16</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>3-6-2013-14</t>
+          <t>2014-03-06</t>
         </is>
       </c>
     </row>
@@ -5835,7 +5902,7 @@
         <v>-6</v>
       </c>
       <c r="AD30" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AE30" t="n">
         <v>25</v>
@@ -5910,7 +5977,7 @@
         <v>28</v>
       </c>
       <c r="BC30" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BD30" t="n">
         <v>10</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>3-6-2013-14</t>
+          <t>2014-03-06</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6084,7 @@
         <v>0.9</v>
       </c>
       <c r="AD31" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AE31" t="n">
         <v>14</v>
@@ -6047,7 +6114,7 @@
         <v>18</v>
       </c>
       <c r="AN31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO31" t="n">
         <v>28</v>
@@ -6065,7 +6132,7 @@
         <v>18</v>
       </c>
       <c r="AT31" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AU31" t="n">
         <v>7</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>3-6-2013-14</t>
+          <t>2014-03-06</t>
         </is>
       </c>
     </row>
